--- a/data/excel/ecommerce_analytics_model.xlsx
+++ b/data/excel/ecommerce_analytics_model.xlsx
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Validated clean dataset ready for SQL &amp; Power BI</t>
+          <t>Validated clean dataset ready for SQL &amp; Tableau</t>
         </is>
       </c>
     </row>
